--- a/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
+++ b/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,6 +113,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B6B6B"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="16">
@@ -219,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -306,6 +312,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -673,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B30"/>
+  <dimension ref="B1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -727,21 +736,21 @@
     <row r="9" ht="17.6" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1.  Click a cell in the Categories column. A dropdown appears.</t>
+          <t>1.  Click a cell under "Also about". A dropdown appears with the five categories.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2.  Choose the entry that matches. The list holds each category on its own and the combinations anybody is likely to need.</t>
+          <t>2.  Pick one. If the question is about a second thing, use the next column, and the one after that for a third. Four questions out of 176 need all three.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3.  Leave it empty when the question is only about its own domain. That is the normal case: about three quarters of them.</t>
+          <t>3.  Leave them empty when the question is only about its own domain. That is the normal case: 130 of the 176.</t>
         </is>
       </c>
     </row>
@@ -749,88 +758,96 @@
     <row r="13" ht="60" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>If you need a combination the list does not hold, type it, separated by commas. The tool checks every name when it reads this file and refuses the whole import if one is not recognised, naming the question it was in. A category nobody recognises would otherwise score nothing, on every screen, and never be noticed.</t>
+          <t>Three columns and not one because neither Google Sheets nor Excel has a dropdown you can pick more than one thing from. Putting the combinations into a single list does not work either: a dropdown list is itself comma separated, so "Security, Privacy" splits into two entries. Three columns sharing one list is the shape that works with nothing typed, and nothing typed means nothing mistyped.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="8" customHeight="1"/>
-    <row r="15" ht="22.4" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="15" ht="45" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>If you do type into these cells, the tool checks every name when it reads this file and refuses the whole import if one is not recognised, naming the question it was in. A category nobody recognises would otherwise score nothing, on every screen, and never be noticed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="8" customHeight="1"/>
+    <row r="17" ht="22.4" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>The nine categories</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Four are the domains themselves, filled in by the tab a question is on: Business, Data, Application, Technology.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Five are what the Categories column asks for: Security, Privacy, Financial, Accessibility, Official Languages.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="8" customHeight="1"/>
-    <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="45" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>A question can carry as many as apply. It still counts once in the overall score, through its domain, and at full weight inside every category it carries. So the category scores do not add up to the overall, and the tool says so.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="22.4" customHeight="1">
-      <c r="B21" s="5" t="inlineStr">
+    <row r="22" ht="8" customHeight="1"/>
+    <row r="23" ht="22.4" customHeight="1">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Never duplicate a question onto a second tab</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>A question that appears on two tabs is counted twice in the overall score, and the department’s number moves because of how we filed a question. One question, one tab, as many categories as apply.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="8" customHeight="1"/>
-    <row r="24" ht="22.4" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="22.4" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Two categories rest on very little</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Accessibility is asked about by three questions and Official Languages by two. That is thin, and it is worth knowing before anybody reads a score for either: a number built on two questions moves a long way on one answer. If there should be more, that is a gap in the instrument and not in this column.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="8" customHeight="1"/>
-    <row r="27" ht="45" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="8" customHeight="1"/>
+    <row r="29" ht="45" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>An earlier version of this workbook said both were empty. That was wrong. Six questions mention something "accessible" and three of them are about accessibility; the other three are the FAIR principles’ Accessible and data reaching other departments, which is a different sense of the word.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29" ht="22.4" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="22.4" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>The Answer type column</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Ten of the 176 questions read as yes or no rather than as a maturity, which you named yourself. The Answer type column says which we think each one is, and the Answer column beside it offers the matching picker: 0 to 10 for a scale question, Yes and No for the others, and N/A on both. Our reading is provisional; change the type and the picker follows.</t>
         </is>
@@ -847,17 +864,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -892,25 +911,35 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Also about</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">and </t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>Answer type</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Maturity Label</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -940,14 +969,16 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -962,14 +993,16 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -984,14 +1017,16 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -1006,14 +1041,16 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -1028,14 +1065,16 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -1050,14 +1089,16 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -1072,14 +1113,16 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -1098,14 +1141,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -1124,14 +1169,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr"/>
@@ -1146,14 +1193,16 @@
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr"/>
@@ -1168,14 +1217,16 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -1190,14 +1241,16 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -1212,14 +1265,16 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -1235,17 +1290,27 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Privacy, Accessibility, Official Languages</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Official Languages</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -1271,14 +1336,16 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -1297,14 +1364,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -1319,14 +1388,16 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -1341,14 +1412,16 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -1363,14 +1436,16 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -1385,14 +1460,16 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -1407,14 +1484,16 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -1433,14 +1512,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -1455,14 +1536,16 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -1477,14 +1560,16 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -1499,14 +1584,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -1521,14 +1608,16 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -1543,14 +1632,16 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -1576,14 +1667,16 @@
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -1598,14 +1691,16 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -1620,14 +1715,16 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -1642,14 +1739,16 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -1664,14 +1763,16 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -1686,14 +1787,16 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -1708,14 +1811,16 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr"/>
@@ -1730,14 +1835,16 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
+      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -1752,14 +1859,16 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
@@ -1785,14 +1894,16 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -1807,14 +1918,16 @@
         </is>
       </c>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H45" s="15" t="n"/>
+      <c r="I45" s="15" t="n"/>
+      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -1833,14 +1946,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -1855,14 +1970,16 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H47" s="15" t="n"/>
+      <c r="I47" s="15" t="n"/>
+      <c r="J47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr"/>
@@ -1877,14 +1994,16 @@
         </is>
       </c>
       <c r="D48" s="13" t="n"/>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="n"/>
-      <c r="G48" s="15" t="n"/>
+      <c r="E48" s="13" t="n"/>
+      <c r="F48" s="13" t="n"/>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H48" s="15" t="n"/>
+      <c r="I48" s="15" t="n"/>
+      <c r="J48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr"/>
@@ -1899,14 +2018,16 @@
         </is>
       </c>
       <c r="D49" s="13" t="n"/>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="n"/>
-      <c r="G49" s="15" t="n"/>
+      <c r="E49" s="13" t="n"/>
+      <c r="F49" s="13" t="n"/>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H49" s="15" t="n"/>
+      <c r="I49" s="15" t="n"/>
+      <c r="J49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr"/>
@@ -1921,14 +2042,16 @@
         </is>
       </c>
       <c r="D50" s="13" t="n"/>
-      <c r="E50" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F50" s="15" t="n"/>
-      <c r="G50" s="15" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H50" s="15" t="n"/>
+      <c r="I50" s="15" t="n"/>
+      <c r="J50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr"/>
@@ -1947,14 +2070,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="n"/>
-      <c r="G51" s="15" t="n"/>
+      <c r="E51" s="13" t="n"/>
+      <c r="F51" s="13" t="n"/>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H51" s="15" t="n"/>
+      <c r="I51" s="15" t="n"/>
+      <c r="J51" s="15" t="n"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
@@ -1980,14 +2105,16 @@
         </is>
       </c>
       <c r="D53" s="13" t="n"/>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F53" s="15" t="n"/>
-      <c r="G53" s="15" t="n"/>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="13" t="n"/>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H53" s="15" t="n"/>
+      <c r="I53" s="15" t="n"/>
+      <c r="J53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr"/>
@@ -2002,14 +2129,16 @@
         </is>
       </c>
       <c r="D54" s="13" t="n"/>
-      <c r="E54" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F54" s="15" t="n"/>
-      <c r="G54" s="15" t="n"/>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="13" t="n"/>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H54" s="15" t="n"/>
+      <c r="I54" s="15" t="n"/>
+      <c r="J54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr"/>
@@ -2028,14 +2157,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F55" s="15" t="n"/>
-      <c r="G55" s="15" t="n"/>
+      <c r="E55" s="13" t="n"/>
+      <c r="F55" s="13" t="n"/>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H55" s="15" t="n"/>
+      <c r="I55" s="15" t="n"/>
+      <c r="J55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr"/>
@@ -2050,14 +2181,16 @@
         </is>
       </c>
       <c r="D56" s="13" t="n"/>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F56" s="15" t="n"/>
-      <c r="G56" s="15" t="n"/>
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="13" t="n"/>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H56" s="15" t="n"/>
+      <c r="I56" s="15" t="n"/>
+      <c r="J56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr"/>
@@ -2072,14 +2205,16 @@
         </is>
       </c>
       <c r="D57" s="13" t="n"/>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="n"/>
-      <c r="G57" s="15" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H57" s="15" t="n"/>
+      <c r="I57" s="15" t="n"/>
+      <c r="J57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr"/>
@@ -2098,14 +2233,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr">
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F58" s="15" t="n"/>
-      <c r="G58" s="15" t="n"/>
       <c r="H58" s="15" t="n"/>
+      <c r="I58" s="15" t="n"/>
+      <c r="J58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr"/>
@@ -2120,14 +2257,16 @@
         </is>
       </c>
       <c r="D59" s="13" t="n"/>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F59" s="15" t="n"/>
-      <c r="G59" s="15" t="n"/>
+      <c r="E59" s="13" t="n"/>
+      <c r="F59" s="13" t="n"/>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H59" s="15" t="n"/>
+      <c r="I59" s="15" t="n"/>
+      <c r="J59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr"/>
@@ -2142,14 +2281,16 @@
         </is>
       </c>
       <c r="D60" s="13" t="n"/>
-      <c r="E60" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="13" t="n"/>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H60" s="15" t="n"/>
+      <c r="I60" s="15" t="n"/>
+      <c r="J60" s="15" t="n"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
@@ -2175,14 +2316,16 @@
         </is>
       </c>
       <c r="D62" s="13" t="n"/>
-      <c r="E62" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F62" s="15" t="n"/>
-      <c r="G62" s="15" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="13" t="n"/>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H62" s="15" t="n"/>
+      <c r="I62" s="15" t="n"/>
+      <c r="J62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr"/>
@@ -2197,14 +2340,16 @@
         </is>
       </c>
       <c r="D63" s="13" t="n"/>
-      <c r="E63" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="n"/>
-      <c r="G63" s="15" t="n"/>
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="13" t="n"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H63" s="15" t="n"/>
+      <c r="I63" s="15" t="n"/>
+      <c r="J63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr"/>
@@ -2219,14 +2364,16 @@
         </is>
       </c>
       <c r="D64" s="13" t="n"/>
-      <c r="E64" s="17" t="inlineStr">
+      <c r="E64" s="13" t="n"/>
+      <c r="F64" s="13" t="n"/>
+      <c r="G64" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F64" s="15" t="n"/>
-      <c r="G64" s="15" t="n"/>
       <c r="H64" s="15" t="n"/>
+      <c r="I64" s="15" t="n"/>
+      <c r="J64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr"/>
@@ -2241,14 +2388,16 @@
         </is>
       </c>
       <c r="D65" s="13" t="n"/>
-      <c r="E65" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="n"/>
-      <c r="G65" s="15" t="n"/>
+      <c r="E65" s="13" t="n"/>
+      <c r="F65" s="13" t="n"/>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H65" s="15" t="n"/>
+      <c r="I65" s="15" t="n"/>
+      <c r="J65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr"/>
@@ -2264,17 +2413,23 @@
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>Accessibility, Official Languages</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="n"/>
-      <c r="G66" s="15" t="n"/>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>Official Languages</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="n"/>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H66" s="15" t="n"/>
+      <c r="I66" s="15" t="n"/>
+      <c r="J66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr"/>
@@ -2289,14 +2444,16 @@
         </is>
       </c>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="17" t="inlineStr">
+      <c r="E67" s="13" t="n"/>
+      <c r="F67" s="13" t="n"/>
+      <c r="G67" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F67" s="15" t="n"/>
-      <c r="G67" s="15" t="n"/>
       <c r="H67" s="15" t="n"/>
+      <c r="I67" s="15" t="n"/>
+      <c r="J67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr"/>
@@ -2311,14 +2468,16 @@
         </is>
       </c>
       <c r="D68" s="13" t="n"/>
-      <c r="E68" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F68" s="15" t="n"/>
-      <c r="G68" s="15" t="n"/>
+      <c r="E68" s="13" t="n"/>
+      <c r="F68" s="13" t="n"/>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H68" s="15" t="n"/>
+      <c r="I68" s="15" t="n"/>
+      <c r="J68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr"/>
@@ -2337,14 +2496,16 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E69" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="n"/>
-      <c r="G69" s="15" t="n"/>
+      <c r="E69" s="13" t="n"/>
+      <c r="F69" s="13" t="n"/>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H69" s="15" t="n"/>
+      <c r="I69" s="15" t="n"/>
+      <c r="J69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr"/>
@@ -2359,37 +2520,45 @@
         </is>
       </c>
       <c r="D70" s="13" t="n"/>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F70" s="15" t="n"/>
-      <c r="G70" s="15" t="n"/>
+      <c r="E70" s="13" t="n"/>
+      <c r="F70" s="13" t="n"/>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H70" s="15" t="n"/>
+      <c r="I70" s="15" t="n"/>
+      <c r="J70" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="Pick the subjects this question is also about, beyond its own domain. Leave it empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages,Security, Privacy,Security, Financial,Privacy, Financial,Accessibility, Official Languages,Privacy, Accessibility, Official Languages,Security, Privacy, Financial"</formula1>
+  <dataValidations count="6">
+    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F34 F35 F36 F37 F38 F39 F40 F41 F42 F44 F45 F46 F47 F48 F49 F50 F51 F53 F54 F55 F56 F57 F59 F60 F62 F63 F65 F66 F68 F69 F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H34 H35 H36 H37 H38 H39 H40 H41 H42 H44 H45 H46 H47 H48 H49 H50 H51 H53 H54 H55 H56 H57 H59 H60 H62 H63 H65 H66 H68 H69 H70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="F58 F64 F67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H58 H64 H67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2403,17 +2572,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2448,25 +2619,35 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Also about</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">and </t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>Answer type</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Maturity Label</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -2496,14 +2677,16 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -2518,14 +2701,16 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -2544,14 +2729,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -2566,14 +2753,16 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -2588,14 +2777,16 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -2610,14 +2801,16 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -2632,14 +2825,16 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -2658,14 +2853,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -2680,14 +2877,16 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -2713,14 +2912,16 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -2735,14 +2936,16 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -2761,14 +2964,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -2783,14 +2988,16 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -2805,14 +3012,16 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -2827,14 +3036,16 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -2849,14 +3060,16 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -2871,14 +3084,16 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -2893,14 +3108,16 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -2915,14 +3132,16 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -2937,14 +3156,16 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -2959,14 +3180,16 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -2996,14 +3219,16 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -3022,14 +3247,16 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -3044,14 +3271,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -3070,14 +3299,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -3096,14 +3327,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -3119,17 +3352,23 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Security, Privacy</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr"/>
@@ -3148,14 +3387,16 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -3174,14 +3415,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -3200,14 +3443,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
@@ -3233,14 +3478,16 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -3255,14 +3502,16 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -3281,14 +3530,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
@@ -3314,14 +3565,16 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -3336,14 +3589,16 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -3358,14 +3613,16 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -3384,14 +3641,16 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H45" s="15" t="n"/>
+      <c r="I45" s="15" t="n"/>
+      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -3410,14 +3669,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -3432,36 +3693,44 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H47" s="15" t="n"/>
+      <c r="I47" s="15" t="n"/>
+      <c r="J47" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A41:J41"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="Pick the subjects this question is also about, beyond its own domain. Leave it empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages,Security, Privacy,Security, Financial,Privacy, Financial,Accessibility, Official Languages,Privacy, Accessibility, Official Languages,Security, Privacy, Financial"</formula1>
+  <dataValidations count="6">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F29 F30 F31 F32 F33 F34 F36 F38 F39 F40 F42 F43 F44 F45 F46 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H29 H30 H31 H32 H33 H34 H36 H38 H39 H40 H42 H43 H44 H45 H46 H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="F28 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H28 H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3475,17 +3744,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3520,25 +3791,35 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Also about</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">and </t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>Answer type</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Maturity Label</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -3568,14 +3849,16 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -3590,14 +3873,16 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -3612,14 +3897,16 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -3634,14 +3921,16 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -3660,14 +3949,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -3682,14 +3973,16 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -3704,14 +3997,16 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -3726,14 +4021,16 @@
         </is>
       </c>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -3748,14 +4045,16 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -3781,14 +4080,16 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -3803,14 +4104,16 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -3825,14 +4128,16 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -3847,14 +4152,16 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -3869,14 +4176,16 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -3891,14 +4200,16 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -3913,14 +4224,16 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -3935,14 +4248,16 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -3957,14 +4272,16 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -3979,14 +4296,16 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -4016,14 +4335,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -4042,14 +4363,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -4064,14 +4387,16 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -4090,14 +4415,16 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -4112,14 +4439,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -4134,14 +4463,16 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -4156,14 +4487,16 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -4178,14 +4511,16 @@
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -4212,17 +4547,23 @@
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Security, Privacy</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -4241,14 +4582,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -4263,14 +4606,16 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -4289,14 +4634,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -4315,14 +4662,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -4337,14 +4686,16 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr"/>
@@ -4363,14 +4714,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
+      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -4385,14 +4738,16 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -4407,14 +4762,16 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -4433,35 +4790,43 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A25:J25"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="Pick the subjects this question is also about, beyond its own domain. Leave it empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages,Security, Privacy,Security, Financial,Privacy, Financial,Accessibility, Official Languages,Privacy, Accessibility, Official Languages,Security, Privacy, Financial"</formula1>
+  <dataValidations count="6">
+    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F26 F27 F28 F31 F32 F33 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H26 H27 H28 H31 H32 H33 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H29 H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4475,17 +4840,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4520,25 +4887,35 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Also about</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">and </t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>Answer type</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Maturity Label</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -4568,14 +4945,16 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -4590,14 +4969,16 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -4612,14 +4993,16 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -4634,14 +5017,16 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -4656,14 +5041,16 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -4678,14 +5065,16 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -4700,14 +5089,16 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -4733,14 +5124,16 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr"/>
@@ -4759,14 +5152,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr"/>
@@ -4781,14 +5176,16 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -4803,14 +5200,16 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -4825,14 +5224,16 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -4847,14 +5248,16 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -4869,14 +5272,16 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -4891,14 +5296,16 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -4913,14 +5320,16 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -4935,14 +5344,16 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -4968,14 +5379,16 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -4990,14 +5403,16 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -5012,14 +5427,16 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -5034,14 +5451,16 @@
         </is>
       </c>
       <c r="D27" s="13" t="n"/>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -5060,14 +5479,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -5082,14 +5503,16 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -5104,14 +5527,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
@@ -5137,14 +5562,16 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -5163,14 +5590,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr"/>
@@ -5189,14 +5618,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -5215,14 +5646,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -5241,14 +5674,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -5267,14 +5702,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -5289,14 +5726,16 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -5315,14 +5754,16 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
@@ -5348,14 +5789,16 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
+      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -5370,14 +5813,16 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -5396,14 +5841,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -5418,14 +5865,16 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -5444,14 +5893,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H45" s="15" t="n"/>
+      <c r="I45" s="15" t="n"/>
+      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -5470,14 +5921,16 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
       <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -5492,36 +5945,44 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H47" s="15" t="n"/>
+      <c r="I47" s="15" t="n"/>
+      <c r="J47" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="Pick the subjects this question is also about, beyond its own domain. Leave it empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages,Security, Privacy,Security, Financial,Privacy, Financial,Accessibility, Official Languages,Privacy, Accessibility, Official Languages,Security, Privacy, Financial"</formula1>
+  <dataValidations count="6">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F20 F21 F22 F24 F25 F26 F27 F28 F29 F30 F32 F33 F34 F35 F37 F38 F39 F41 F42 F43 F44 F45 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H13 H14 H15 H16 H17 H18 H20 H21 H22 H24 H25 H26 H27 H28 H29 H30 H32 H33 H34 H35 H37 H38 H39 H41 H42 H43 H44 H45 H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="F19 F36 F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H19 H36 H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5829,7 +6290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6043,6 +6504,13 @@
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="12" t="n"/>
     </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>This tab is your own Summary Dashboard, reproduced so nothing is missing from this copy. It does not calculate here: this workbook is for the Categories columns, and the scoring happens in the tool.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
+++ b/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
@@ -682,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B32"/>
+  <dimension ref="B1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -736,118 +736,103 @@
     <row r="9" ht="17.6" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1.  Click a cell under "Also about". A dropdown appears with the five categories.</t>
+          <t>1.  Click a cell in the Categories column. A dropdown appears with the five.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2.  Pick one. If the question is about a second thing, use the next column, and the one after that for a third. Four questions out of 176 need all three.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>3.  Leave them empty when the question is only about its own domain. That is the normal case: 130 of the 176.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="8" customHeight="1"/>
-    <row r="13" ht="60" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Three columns and not one because neither Google Sheets nor Excel has a dropdown you can pick more than one thing from. Putting the combinations into a single list does not work either: a dropdown list is itself comma separated, so "Security, Privacy" splits into two entries. Three columns sharing one list is the shape that works with nothing typed, and nothing typed means nothing mistyped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="8" customHeight="1"/>
-    <row r="15" ht="45" customHeight="1">
+          <t>2.  Tick as many as apply. Most questions need none; 130 of the 176 stay empty, which means "this one is only about its own domain".</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="8" customHeight="1"/>
+    <row r="12" ht="45" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>If you do type into these cells instead, the tool checks every name when it reads this file and refuses the whole import if one is not recognised, naming the question it was in. A category nobody recognises would otherwise score nothing, on every screen, and never be noticed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="22.4" customHeight="1">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>The nine categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>If you do type into these cells, the tool checks every name when it reads this file and refuses the whole import if one is not recognised, naming the question it was in. A category nobody recognises would otherwise score nothing, on every screen, and never be noticed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="8" customHeight="1"/>
-    <row r="17" ht="22.4" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>The nine categories</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t>Four are the domains themselves, filled in by the tab a question is on: Business, Data, Application, Technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Five are what the Categories column asks for: Security, Privacy, Financial, Accessibility, Official Languages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="8" customHeight="1"/>
+    <row r="18" ht="45" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Four are the domains themselves, filled in by the tab a question is on: Business, Data, Application, Technology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Five are what the Categories column asks for: Security, Privacy, Financial, Accessibility, Official Languages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="45" customHeight="1">
+          <t>A question can carry as many as apply. It still counts once in the overall score, through its domain, and at full weight inside every category it carries. So the category scores do not add up to the overall, and the tool says so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="8" customHeight="1"/>
+    <row r="20" ht="22.4" customHeight="1">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Never duplicate a question onto a second tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>A question can carry as many as apply. It still counts once in the overall score, through its domain, and at full weight inside every category it carries. So the category scores do not add up to the overall, and the tool says so.</t>
+          <t>A question that appears on two tabs is counted twice in the overall score, and the department’s number moves because of how we filed a question. One question, one tab, as many categories as apply.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1"/>
     <row r="23" ht="22.4" customHeight="1">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Never duplicate a question onto a second tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Two categories rest on very little</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>A question that appears on two tabs is counted twice in the overall score, and the department’s number moves because of how we filed a question. One question, one tab, as many categories as apply.</t>
+          <t>Accessibility is asked about by three questions and Official Languages by two. That is thin, and it is worth knowing before anybody reads a score for either: a number built on two questions moves a long way on one answer. If there should be more, that is a gap in the instrument and not in this column.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="8" customHeight="1"/>
-    <row r="26" ht="22.4" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Two categories rest on very little</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Accessibility is asked about by three questions and Official Languages by two. That is thin, and it is worth knowing before anybody reads a score for either: a number built on two questions moves a long way on one answer. If there should be more, that is a gap in the instrument and not in this column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29" ht="45" customHeight="1">
+    <row r="26" ht="45" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>An earlier version of this workbook said both were empty. That was wrong. Six questions mention something "accessible" and three of them are about accessibility; the other three are the FAIR principles’ Accessible and data reaching other departments, which is a different sense of the word.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="8" customHeight="1"/>
+    <row r="28" ht="22.4" customHeight="1">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>The Answer type column</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>An earlier version of this workbook said both were empty. That was wrong. Six questions mention something "accessible" and three of them are about accessibility; the other three are the FAIR principles’ Accessible and data reaching other departments, which is a different sense of the word.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="22.4" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>The Answer type column</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Ten of the 176 questions read as yes or no rather than as a maturity, which you named yourself. The Answer type column says which we think each one is, and the Answer column beside it offers the matching picker: 0 to 10 for a scale question, Yes and No for the others, and N/A on both. Our reading is provisional; change the type and the picker follows.</t>
         </is>
@@ -864,19 +849,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -911,35 +894,25 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Also about</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Answer type</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">and </t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Answer type</t>
+          <t>Maturity Label</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Maturity Label</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -969,16 +942,14 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -993,16 +964,14 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -1017,16 +986,14 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -1041,16 +1008,14 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -1065,16 +1030,14 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -1089,16 +1052,14 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -1113,16 +1074,14 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -1141,16 +1100,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -1169,16 +1126,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr"/>
@@ -1193,16 +1148,14 @@
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr"/>
@@ -1217,16 +1170,14 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -1241,16 +1192,14 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -1265,16 +1214,14 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -1290,27 +1237,17 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Privacy</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>Official Languages</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+          <t>Privacy, Accessibility, Official Languages</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -1336,16 +1273,14 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -1364,16 +1299,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -1388,16 +1321,14 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -1412,16 +1343,14 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
       <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -1436,16 +1365,14 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -1460,16 +1387,14 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
       <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -1484,16 +1409,14 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -1512,16 +1435,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -1536,16 +1457,14 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -1560,16 +1479,14 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -1584,16 +1501,14 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -1608,16 +1523,14 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
       <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -1632,16 +1545,14 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -1667,16 +1578,14 @@
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -1691,16 +1600,14 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -1715,16 +1622,14 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -1739,16 +1644,14 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
       <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -1763,16 +1666,14 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -1787,16 +1688,14 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -1811,16 +1710,14 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
       <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr"/>
@@ -1835,16 +1732,14 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -1859,16 +1754,14 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
@@ -1894,16 +1787,14 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -1918,16 +1809,14 @@
         </is>
       </c>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="15" t="n"/>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -1946,16 +1835,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -1970,16 +1857,14 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr"/>
@@ -1994,16 +1879,14 @@
         </is>
       </c>
       <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="n"/>
+      <c r="G48" s="15" t="n"/>
       <c r="H48" s="15" t="n"/>
-      <c r="I48" s="15" t="n"/>
-      <c r="J48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr"/>
@@ -2018,16 +1901,14 @@
         </is>
       </c>
       <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="n"/>
+      <c r="G49" s="15" t="n"/>
       <c r="H49" s="15" t="n"/>
-      <c r="I49" s="15" t="n"/>
-      <c r="J49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr"/>
@@ -2042,16 +1923,14 @@
         </is>
       </c>
       <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="n"/>
+      <c r="G50" s="15" t="n"/>
       <c r="H50" s="15" t="n"/>
-      <c r="I50" s="15" t="n"/>
-      <c r="J50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr"/>
@@ -2070,16 +1949,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="15" t="n"/>
       <c r="H51" s="15" t="n"/>
-      <c r="I51" s="15" t="n"/>
-      <c r="J51" s="15" t="n"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
@@ -2105,16 +1982,14 @@
         </is>
       </c>
       <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="n"/>
+      <c r="G53" s="15" t="n"/>
       <c r="H53" s="15" t="n"/>
-      <c r="I53" s="15" t="n"/>
-      <c r="J53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr"/>
@@ -2129,16 +2004,14 @@
         </is>
       </c>
       <c r="D54" s="13" t="n"/>
-      <c r="E54" s="13" t="n"/>
-      <c r="F54" s="13" t="n"/>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="n"/>
+      <c r="G54" s="15" t="n"/>
       <c r="H54" s="15" t="n"/>
-      <c r="I54" s="15" t="n"/>
-      <c r="J54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr"/>
@@ -2157,16 +2030,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
       <c r="H55" s="15" t="n"/>
-      <c r="I55" s="15" t="n"/>
-      <c r="J55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr"/>
@@ -2181,16 +2052,14 @@
         </is>
       </c>
       <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="n"/>
+      <c r="G56" s="15" t="n"/>
       <c r="H56" s="15" t="n"/>
-      <c r="I56" s="15" t="n"/>
-      <c r="J56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr"/>
@@ -2205,16 +2074,14 @@
         </is>
       </c>
       <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="n"/>
+      <c r="G57" s="15" t="n"/>
       <c r="H57" s="15" t="n"/>
-      <c r="I57" s="15" t="n"/>
-      <c r="J57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr"/>
@@ -2233,16 +2100,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
-      <c r="G58" s="17" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F58" s="15" t="n"/>
+      <c r="G58" s="15" t="n"/>
       <c r="H58" s="15" t="n"/>
-      <c r="I58" s="15" t="n"/>
-      <c r="J58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr"/>
@@ -2257,16 +2122,14 @@
         </is>
       </c>
       <c r="D59" s="13" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="13" t="n"/>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="n"/>
+      <c r="G59" s="15" t="n"/>
       <c r="H59" s="15" t="n"/>
-      <c r="I59" s="15" t="n"/>
-      <c r="J59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr"/>
@@ -2281,16 +2144,14 @@
         </is>
       </c>
       <c r="D60" s="13" t="n"/>
-      <c r="E60" s="13" t="n"/>
-      <c r="F60" s="13" t="n"/>
-      <c r="G60" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="n"/>
+      <c r="G60" s="15" t="n"/>
       <c r="H60" s="15" t="n"/>
-      <c r="I60" s="15" t="n"/>
-      <c r="J60" s="15" t="n"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
@@ -2316,16 +2177,14 @@
         </is>
       </c>
       <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="n"/>
+      <c r="G62" s="15" t="n"/>
       <c r="H62" s="15" t="n"/>
-      <c r="I62" s="15" t="n"/>
-      <c r="J62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr"/>
@@ -2340,16 +2199,14 @@
         </is>
       </c>
       <c r="D63" s="13" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="13" t="n"/>
-      <c r="G63" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="n"/>
+      <c r="G63" s="15" t="n"/>
       <c r="H63" s="15" t="n"/>
-      <c r="I63" s="15" t="n"/>
-      <c r="J63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr"/>
@@ -2364,16 +2221,14 @@
         </is>
       </c>
       <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="13" t="n"/>
-      <c r="G64" s="17" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F64" s="15" t="n"/>
+      <c r="G64" s="15" t="n"/>
       <c r="H64" s="15" t="n"/>
-      <c r="I64" s="15" t="n"/>
-      <c r="J64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr"/>
@@ -2388,16 +2243,14 @@
         </is>
       </c>
       <c r="D65" s="13" t="n"/>
-      <c r="E65" s="13" t="n"/>
-      <c r="F65" s="13" t="n"/>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="n"/>
+      <c r="G65" s="15" t="n"/>
       <c r="H65" s="15" t="n"/>
-      <c r="I65" s="15" t="n"/>
-      <c r="J65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr"/>
@@ -2413,23 +2266,17 @@
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="E66" s="16" t="inlineStr">
-        <is>
-          <t>Official Languages</t>
-        </is>
-      </c>
-      <c r="F66" s="13" t="n"/>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+          <t>Accessibility, Official Languages</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="n"/>
+      <c r="G66" s="15" t="n"/>
       <c r="H66" s="15" t="n"/>
-      <c r="I66" s="15" t="n"/>
-      <c r="J66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr"/>
@@ -2444,16 +2291,14 @@
         </is>
       </c>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
-      <c r="G67" s="17" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F67" s="15" t="n"/>
+      <c r="G67" s="15" t="n"/>
       <c r="H67" s="15" t="n"/>
-      <c r="I67" s="15" t="n"/>
-      <c r="J67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr"/>
@@ -2468,16 +2313,14 @@
         </is>
       </c>
       <c r="D68" s="13" t="n"/>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F68" s="15" t="n"/>
+      <c r="G68" s="15" t="n"/>
       <c r="H68" s="15" t="n"/>
-      <c r="I68" s="15" t="n"/>
-      <c r="J68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr"/>
@@ -2496,16 +2339,14 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E69" s="13" t="n"/>
-      <c r="F69" s="13" t="n"/>
-      <c r="G69" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="n"/>
+      <c r="G69" s="15" t="n"/>
       <c r="H69" s="15" t="n"/>
-      <c r="I69" s="15" t="n"/>
-      <c r="J69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr"/>
@@ -2520,45 +2361,37 @@
         </is>
       </c>
       <c r="D70" s="13" t="n"/>
-      <c r="E70" s="13" t="n"/>
-      <c r="F70" s="13" t="n"/>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="n"/>
+      <c r="G70" s="15" t="n"/>
       <c r="H70" s="15" t="n"/>
-      <c r="I70" s="15" t="n"/>
-      <c r="J70" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A61:J61"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A61:H61"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H34 H35 H36 H37 H38 H39 H40 H41 H42 H44 H45 H46 H47 H48 H49 H50 H51 H53 H54 H55 H56 H57 H59 H60 H62 H63 H65 H66 H68 H69 H70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F34 F35 F36 F37 F38 F39 F40 F41 F42 F44 F45 F46 F47 F48 F49 F50 F51 F53 F54 F55 F56 F57 F59 F60 F62 F63 F65 F66 F68 F69 F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="H58 H64 H67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F58 F64 F67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2572,19 +2405,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2619,35 +2450,25 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Also about</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Answer type</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">and </t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Answer type</t>
+          <t>Maturity Label</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Maturity Label</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -2677,16 +2498,14 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -2701,16 +2520,14 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -2729,16 +2546,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -2753,16 +2568,14 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -2777,16 +2590,14 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -2801,16 +2612,14 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -2825,16 +2634,14 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -2853,16 +2660,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -2877,16 +2682,14 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -2912,16 +2715,14 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -2936,16 +2737,14 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -2964,16 +2763,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -2988,16 +2785,14 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -3012,16 +2807,14 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -3036,16 +2829,14 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -3060,16 +2851,14 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -3084,16 +2873,14 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -3108,16 +2895,14 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
       <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -3132,16 +2917,14 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -3156,16 +2939,14 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
       <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -3180,16 +2961,14 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -3219,16 +2998,14 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -3247,16 +3024,14 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -3271,16 +3046,14 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -3299,16 +3072,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
       <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -3327,16 +3098,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -3352,23 +3121,17 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>Privacy</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+          <t>Security, Privacy</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
       <c r="H33" s="15" t="n"/>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr"/>
@@ -3387,16 +3150,14 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -3415,16 +3176,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -3443,16 +3202,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
@@ -3478,16 +3235,14 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -3502,16 +3257,14 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -3530,16 +3283,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
       <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
@@ -3565,16 +3316,14 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -3589,16 +3338,14 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -3613,16 +3360,14 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -3641,16 +3386,14 @@
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="15" t="n"/>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -3669,16 +3412,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -3693,44 +3434,36 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H29 H30 H31 H32 H33 H34 H36 H38 H39 H40 H42 H43 H44 H45 H46 H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F29 F30 F31 F32 F33 F34 F36 F38 F39 F40 F42 F43 F44 F45 F46 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="H28 H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F28 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3744,19 +3477,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3791,35 +3522,25 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Also about</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Answer type</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">and </t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Answer type</t>
+          <t>Maturity Label</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Maturity Label</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -3849,16 +3570,14 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -3873,16 +3592,14 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -3897,16 +3614,14 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -3921,16 +3636,14 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -3949,16 +3662,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -3973,16 +3684,14 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -3997,16 +3706,14 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -4021,16 +3728,14 @@
         </is>
       </c>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -4045,16 +3750,14 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -4080,16 +3783,14 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -4104,16 +3805,14 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -4128,16 +3827,14 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -4152,16 +3849,14 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -4176,16 +3871,14 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -4200,16 +3893,14 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -4224,16 +3915,14 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -4248,16 +3937,14 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -4272,16 +3959,14 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
       <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -4296,16 +3981,14 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -4335,16 +4018,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -4363,16 +4044,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -4387,16 +4066,14 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -4415,16 +4092,14 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -4439,16 +4114,14 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -4463,16 +4136,14 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
       <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -4487,16 +4158,14 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -4511,16 +4180,14 @@
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
       <c r="H33" s="15" t="n"/>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -4547,23 +4214,17 @@
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>Privacy</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+          <t>Security, Privacy</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -4582,16 +4243,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -4606,16 +4265,14 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
       <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -4634,16 +4291,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -4662,16 +4317,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -4686,16 +4339,14 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
       <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr"/>
@@ -4714,16 +4365,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -4738,16 +4387,14 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -4762,16 +4409,14 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -4790,43 +4435,35 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H26 H27 H28 H31 H32 H33 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F26 F27 F28 F31 F32 F33 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="H29 H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4840,19 +4477,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4887,35 +4522,25 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Also about</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Answer type</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">and </t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Answer type</t>
+          <t>Maturity Label</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Maturity Label</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -4945,16 +4570,14 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -4969,16 +4592,14 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -4993,16 +4614,14 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -5017,16 +4636,14 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -5041,16 +4658,14 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -5065,16 +4680,14 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -5089,16 +4702,14 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -5124,16 +4735,14 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr"/>
@@ -5152,16 +4761,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr"/>
@@ -5176,16 +4783,14 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -5200,16 +4805,14 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -5224,16 +4827,14 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -5248,16 +4849,14 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -5272,16 +4871,14 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -5296,16 +4893,14 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -5320,16 +4915,14 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -5344,16 +4937,14 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -5379,16 +4970,14 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -5403,16 +4992,14 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
       <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -5427,16 +5014,14 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -5451,16 +5036,14 @@
         </is>
       </c>
       <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -5479,16 +5062,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -5503,16 +5084,14 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -5527,16 +5106,14 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
@@ -5562,16 +5139,14 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -5590,16 +5165,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
       <c r="H33" s="15" t="n"/>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr"/>
@@ -5618,16 +5191,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -5646,16 +5217,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -5674,16 +5243,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -5702,16 +5269,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
       <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -5726,16 +5291,14 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -5754,16 +5317,14 @@
           <t>Security</t>
         </is>
       </c>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
@@ -5789,16 +5350,14 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -5813,16 +5372,14 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -5841,16 +5398,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -5865,16 +5420,14 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -5893,16 +5446,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="15" t="n"/>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -5921,16 +5472,14 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -5945,44 +5494,36 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H13 H14 H15 H16 H17 H18 H20 H21 H22 H24 H25 H26 H27 H28 H29 H30 H32 H33 H34 H35 H37 H38 H39 H41 H42 H43 H44 H45 H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F20 F21 F22 F24 F25 F26 F27 F28 F29 F30 F32 F33 F34 F35 F37 F38 F39 F41 F42 F43 F44 F45 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="H19 H36 H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F19 F36 F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
+++ b/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
@@ -2381,18 +2381,15 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A61:H61"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F34 F35 F36 F37 F38 F39 F40 F41 F42 F44 F45 F46 F47 F48 F49 F50 F51 F53 F54 F55 F56 F57 F59 F60 F62 F63 F65 F66 F68 F69 F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
-      <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F58 F64 F67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
-      <formula1>"Yes,No,N/A"</formula1>
+    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+      <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3453,18 +3450,15 @@
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A27:H27"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F29 F30 F31 F32 F33 F34 F36 F38 F39 F40 F42 F43 F44 F45 F46 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
-      <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F28 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
-      <formula1>"Yes,No,N/A"</formula1>
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+      <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4453,18 +4447,15 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F26 F27 F28 F31 F32 F33 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
-      <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
-      <formula1>"Yes,No,N/A"</formula1>
+    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+      <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5513,18 +5504,15 @@
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F20 F21 F22 F24 F25 F26 F27 F28 F29 F30 F32 F33 F34 F35 F37 F38 F39 F41 F42 F43 F44 F45 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
-      <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F19 F36 F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
-      <formula1>"Yes,No,N/A"</formula1>
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+      <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
+++ b/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
@@ -2382,13 +2382,13 @@
     <mergeCell ref="A61:H61"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
+    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3451,13 +3451,13 @@
     <mergeCell ref="A27:H27"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4448,13 +4448,13 @@
     <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
+    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5505,13 +5505,13 @@
     <mergeCell ref="A40:H40"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
+++ b/Deliverables/GC EA assessment tool - categories, filled as an example.xlsx
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -268,6 +268,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -948,7 +951,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="16">
+        <f>IF(OR(F5="",NOT(ISNUMBER(F5))),"",IFERROR(VLOOKUP(F5,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -970,7 +976,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="16">
+        <f>IF(OR(F6="",NOT(ISNUMBER(F6))),"",IFERROR(VLOOKUP(F6,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -992,7 +1001,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="16">
+        <f>IF(OR(F7="",NOT(ISNUMBER(F7))),"",IFERROR(VLOOKUP(F7,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -1014,7 +1026,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="16">
+        <f>IF(OR(F8="",NOT(ISNUMBER(F8))),"",IFERROR(VLOOKUP(F8,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -1036,7 +1051,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="16">
+        <f>IF(OR(F9="",NOT(ISNUMBER(F9))),"",IFERROR(VLOOKUP(F9,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -1058,7 +1076,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="16">
+        <f>IF(OR(F10="",NOT(ISNUMBER(F10))),"",IFERROR(VLOOKUP(F10,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -1080,7 +1101,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="16">
+        <f>IF(OR(F11="",NOT(ISNUMBER(F11))),"",IFERROR(VLOOKUP(F11,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
@@ -1095,7 +1119,7 @@
           <t>How well understood are the total lifecycle costs — including build, operate, maintain, and decommission — of the current solution?</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -1106,7 +1130,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="G12" s="16">
+        <f>IF(OR(F12="",NOT(ISNUMBER(F12))),"",IFERROR(VLOOKUP(F12,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H12" s="15" t="n"/>
     </row>
     <row r="13">
@@ -1121,7 +1148,7 @@
           <t>What are the current unit economics (cost per transaction, cost per entity managed) and how are they tracked?</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -1132,7 +1159,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="G13" s="16">
+        <f>IF(OR(F13="",NOT(ISNUMBER(F13))),"",IFERROR(VLOOKUP(F13,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H13" s="15" t="n"/>
     </row>
     <row r="14">
@@ -1154,7 +1184,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="G14" s="16">
+        <f>IF(OR(F14="",NOT(ISNUMBER(F14))),"",IFERROR(VLOOKUP(F14,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H14" s="15" t="n"/>
     </row>
     <row r="15">
@@ -1176,7 +1209,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",NOT(ISNUMBER(F15))),"",IFERROR(VLOOKUP(F15,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -1198,7 +1234,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",NOT(ISNUMBER(F16))),"",IFERROR(VLOOKUP(F16,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -1220,7 +1259,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",NOT(ISNUMBER(F17))),"",IFERROR(VLOOKUP(F17,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -1235,7 +1277,7 @@
           <t>How are universal requirements — accessibility, official languages, inclusion, and privacy — currently addressed in the solution?</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Privacy, Accessibility, Official Languages</t>
         </is>
@@ -1246,7 +1288,10 @@
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",NOT(ISNUMBER(F18))),"",IFERROR(VLOOKUP(F18,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
@@ -1279,7 +1324,10 @@
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",NOT(ISNUMBER(F20))),"",IFERROR(VLOOKUP(F20,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -1294,7 +1342,7 @@
           <t>Is there a documented business case that articulates the expected value, outcomes, and measurable benefits of the proposed solution?</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -1305,7 +1353,10 @@
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",NOT(ISNUMBER(F21))),"",IFERROR(VLOOKUP(F21,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -1327,7 +1378,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",NOT(ISNUMBER(F22))),"",IFERROR(VLOOKUP(F22,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
@@ -1349,7 +1403,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="G23" s="16">
+        <f>IF(OR(F23="",NOT(ISNUMBER(F23))),"",IFERROR(VLOOKUP(F23,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
@@ -1371,7 +1428,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",NOT(ISNUMBER(F24))),"",IFERROR(VLOOKUP(F24,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
@@ -1393,7 +1453,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="G25" s="16">
+        <f>IF(OR(F25="",NOT(ISNUMBER(F25))),"",IFERROR(VLOOKUP(F25,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H25" s="15" t="n"/>
     </row>
     <row r="26">
@@ -1415,7 +1478,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="G26" s="16">
+        <f>IF(OR(F26="",NOT(ISNUMBER(F26))),"",IFERROR(VLOOKUP(F26,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
@@ -1430,7 +1496,7 @@
           <t>Is there a funding model and sourcing strategy that is sustainable across the full lifecycle of the solution?</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -1441,7 +1507,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="G27" s="16">
+        <f>IF(OR(F27="",NOT(ISNUMBER(F27))),"",IFERROR(VLOOKUP(F27,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H27" s="15" t="n"/>
     </row>
     <row r="28">
@@ -1463,7 +1532,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="G28" s="16">
+        <f>IF(OR(F28="",NOT(ISNUMBER(F28))),"",IFERROR(VLOOKUP(F28,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -1485,7 +1557,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="G29" s="16">
+        <f>IF(OR(F29="",NOT(ISNUMBER(F29))),"",IFERROR(VLOOKUP(F29,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -1507,7 +1582,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="G30" s="16">
+        <f>IF(OR(F30="",NOT(ISNUMBER(F30))),"",IFERROR(VLOOKUP(F30,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
@@ -1529,7 +1607,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="G31" s="16">
+        <f>IF(OR(F31="",NOT(ISNUMBER(F31))),"",IFERROR(VLOOKUP(F31,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
@@ -1551,7 +1632,10 @@
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="G32" s="16">
+        <f>IF(OR(F32="",NOT(ISNUMBER(F32))),"",IFERROR(VLOOKUP(F32,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H32" s="15" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
@@ -1584,7 +1668,10 @@
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="G34" s="16">
+        <f>IF(OR(F34="",NOT(ISNUMBER(F34))),"",IFERROR(VLOOKUP(F34,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H34" s="15" t="n"/>
     </row>
     <row r="35">
@@ -1606,7 +1693,10 @@
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="G35" s="16">
+        <f>IF(OR(F35="",NOT(ISNUMBER(F35))),"",IFERROR(VLOOKUP(F35,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -1628,7 +1718,10 @@
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="G36" s="16">
+        <f>IF(OR(F36="",NOT(ISNUMBER(F36))),"",IFERROR(VLOOKUP(F36,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
@@ -1650,7 +1743,10 @@
         </is>
       </c>
       <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="G37" s="16">
+        <f>IF(OR(F37="",NOT(ISNUMBER(F37))),"",IFERROR(VLOOKUP(F37,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H37" s="15" t="n"/>
     </row>
     <row r="38">
@@ -1672,7 +1768,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="G38" s="16">
+        <f>IF(OR(F38="",NOT(ISNUMBER(F38))),"",IFERROR(VLOOKUP(F38,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -1694,7 +1793,10 @@
         </is>
       </c>
       <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="G39" s="16">
+        <f>IF(OR(F39="",NOT(ISNUMBER(F39))),"",IFERROR(VLOOKUP(F39,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H39" s="15" t="n"/>
     </row>
     <row r="40">
@@ -1716,7 +1818,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="G40" s="16">
+        <f>IF(OR(F40="",NOT(ISNUMBER(F40))),"",IFERROR(VLOOKUP(F40,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H40" s="15" t="n"/>
     </row>
     <row r="41">
@@ -1738,7 +1843,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="G41" s="16">
+        <f>IF(OR(F41="",NOT(ISNUMBER(F41))),"",IFERROR(VLOOKUP(F41,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H41" s="15" t="n"/>
     </row>
     <row r="42">
@@ -1760,7 +1868,10 @@
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="G42" s="16">
+        <f>IF(OR(F42="",NOT(ISNUMBER(F42))),"",IFERROR(VLOOKUP(F42,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H42" s="15" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
@@ -1793,7 +1904,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="G44" s="16">
+        <f>IF(OR(F44="",NOT(ISNUMBER(F44))),"",IFERROR(VLOOKUP(F44,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H44" s="15" t="n"/>
     </row>
     <row r="45">
@@ -1815,7 +1929,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="G45" s="16">
+        <f>IF(OR(F45="",NOT(ISNUMBER(F45))),"",IFERROR(VLOOKUP(F45,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H45" s="15" t="n"/>
     </row>
     <row r="46">
@@ -1830,7 +1947,7 @@
           <t>How well are costs, prices, and unit economics tracked and published, enabling informed investment decisions?</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -1841,7 +1958,10 @@
         </is>
       </c>
       <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="G46" s="16">
+        <f>IF(OR(F46="",NOT(ISNUMBER(F46))),"",IFERROR(VLOOKUP(F46,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H46" s="15" t="n"/>
     </row>
     <row r="47">
@@ -1863,7 +1983,10 @@
         </is>
       </c>
       <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="G47" s="16">
+        <f>IF(OR(F47="",NOT(ISNUMBER(F47))),"",IFERROR(VLOOKUP(F47,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H47" s="15" t="n"/>
     </row>
     <row r="48">
@@ -1885,7 +2008,10 @@
         </is>
       </c>
       <c r="F48" s="15" t="n"/>
-      <c r="G48" s="15" t="n"/>
+      <c r="G48" s="16">
+        <f>IF(OR(F48="",NOT(ISNUMBER(F48))),"",IFERROR(VLOOKUP(F48,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H48" s="15" t="n"/>
     </row>
     <row r="49">
@@ -1907,7 +2033,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n"/>
-      <c r="G49" s="15" t="n"/>
+      <c r="G49" s="16">
+        <f>IF(OR(F49="",NOT(ISNUMBER(F49))),"",IFERROR(VLOOKUP(F49,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H49" s="15" t="n"/>
     </row>
     <row r="50">
@@ -1929,7 +2058,10 @@
         </is>
       </c>
       <c r="F50" s="15" t="n"/>
-      <c r="G50" s="15" t="n"/>
+      <c r="G50" s="16">
+        <f>IF(OR(F50="",NOT(ISNUMBER(F50))),"",IFERROR(VLOOKUP(F50,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H50" s="15" t="n"/>
     </row>
     <row r="51">
@@ -1944,7 +2076,7 @@
           <t>Are periodic evaluations of continuing business need performed to assess whether the solution still justifies its cost?</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -1955,7 +2087,10 @@
         </is>
       </c>
       <c r="F51" s="15" t="n"/>
-      <c r="G51" s="15" t="n"/>
+      <c r="G51" s="16">
+        <f>IF(OR(F51="",NOT(ISNUMBER(F51))),"",IFERROR(VLOOKUP(F51,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H51" s="15" t="n"/>
     </row>
     <row r="52" ht="24" customHeight="1">
@@ -1988,7 +2123,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n"/>
-      <c r="G53" s="15" t="n"/>
+      <c r="G53" s="16">
+        <f>IF(OR(F53="",NOT(ISNUMBER(F53))),"",IFERROR(VLOOKUP(F53,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H53" s="15" t="n"/>
     </row>
     <row r="54">
@@ -2010,7 +2148,10 @@
         </is>
       </c>
       <c r="F54" s="15" t="n"/>
-      <c r="G54" s="15" t="n"/>
+      <c r="G54" s="16">
+        <f>IF(OR(F54="",NOT(ISNUMBER(F54))),"",IFERROR(VLOOKUP(F54,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H54" s="15" t="n"/>
     </row>
     <row r="55">
@@ -2025,7 +2166,7 @@
           <t>Is there an established and confirmed funding strategy, including lifecycle funding beyond the initial build phase?</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -2036,7 +2177,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n"/>
-      <c r="G55" s="15" t="n"/>
+      <c r="G55" s="16">
+        <f>IF(OR(F55="",NOT(ISNUMBER(F55))),"",IFERROR(VLOOKUP(F55,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H55" s="15" t="n"/>
     </row>
     <row r="56">
@@ -2058,7 +2202,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n"/>
-      <c r="G56" s="15" t="n"/>
+      <c r="G56" s="16">
+        <f>IF(OR(F56="",NOT(ISNUMBER(F56))),"",IFERROR(VLOOKUP(F56,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H56" s="15" t="n"/>
     </row>
     <row r="57">
@@ -2080,7 +2227,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n"/>
-      <c r="G57" s="15" t="n"/>
+      <c r="G57" s="16">
+        <f>IF(OR(F57="",NOT(ISNUMBER(F57))),"",IFERROR(VLOOKUP(F57,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H57" s="15" t="n"/>
     </row>
     <row r="58">
@@ -2095,18 +2245,21 @@
           <t>Has a formal threat and risk assessment (including sovereignty and security classification) been completed and reviewed?</t>
         </is>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr">
+      <c r="E58" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F58" s="15" t="n"/>
-      <c r="G58" s="15" t="n"/>
+      <c r="G58" s="16">
+        <f>IF(OR(F58="",NOT(ISNUMBER(F58))),"",IFERROR(VLOOKUP(F58,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H58" s="15" t="n"/>
     </row>
     <row r="59">
@@ -2128,7 +2281,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n"/>
-      <c r="G59" s="15" t="n"/>
+      <c r="G59" s="16">
+        <f>IF(OR(F59="",NOT(ISNUMBER(F59))),"",IFERROR(VLOOKUP(F59,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H59" s="15" t="n"/>
     </row>
     <row r="60">
@@ -2150,7 +2306,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
+      <c r="G60" s="16">
+        <f>IF(OR(F60="",NOT(ISNUMBER(F60))),"",IFERROR(VLOOKUP(F60,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H60" s="15" t="n"/>
     </row>
     <row r="61" ht="24" customHeight="1">
@@ -2183,7 +2342,10 @@
         </is>
       </c>
       <c r="F62" s="15" t="n"/>
-      <c r="G62" s="15" t="n"/>
+      <c r="G62" s="16">
+        <f>IF(OR(F62="",NOT(ISNUMBER(F62))),"",IFERROR(VLOOKUP(F62,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H62" s="15" t="n"/>
     </row>
     <row r="63">
@@ -2205,7 +2367,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n"/>
-      <c r="G63" s="15" t="n"/>
+      <c r="G63" s="16">
+        <f>IF(OR(F63="",NOT(ISNUMBER(F63))),"",IFERROR(VLOOKUP(F63,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H63" s="15" t="n"/>
     </row>
     <row r="64">
@@ -2221,13 +2386,16 @@
         </is>
       </c>
       <c r="D64" s="13" t="n"/>
-      <c r="E64" s="17" t="inlineStr">
+      <c r="E64" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F64" s="15" t="n"/>
-      <c r="G64" s="15" t="n"/>
+      <c r="G64" s="16">
+        <f>IF(OR(F64="",NOT(ISNUMBER(F64))),"",IFERROR(VLOOKUP(F64,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H64" s="15" t="n"/>
     </row>
     <row r="65">
@@ -2249,7 +2417,10 @@
         </is>
       </c>
       <c r="F65" s="15" t="n"/>
-      <c r="G65" s="15" t="n"/>
+      <c r="G65" s="16">
+        <f>IF(OR(F65="",NOT(ISNUMBER(F65))),"",IFERROR(VLOOKUP(F65,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H65" s="15" t="n"/>
     </row>
     <row r="66">
@@ -2264,7 +2435,7 @@
           <t>Are compliance requirements (legal, regulatory, policy, accessibility, bilingualism) formally tracked and verified?</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>Accessibility, Official Languages</t>
         </is>
@@ -2275,7 +2446,10 @@
         </is>
       </c>
       <c r="F66" s="15" t="n"/>
-      <c r="G66" s="15" t="n"/>
+      <c r="G66" s="16">
+        <f>IF(OR(F66="",NOT(ISNUMBER(F66))),"",IFERROR(VLOOKUP(F66,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H66" s="15" t="n"/>
     </row>
     <row r="67">
@@ -2291,13 +2465,16 @@
         </is>
       </c>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="17" t="inlineStr">
+      <c r="E67" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F67" s="15" t="n"/>
-      <c r="G67" s="15" t="n"/>
+      <c r="G67" s="16">
+        <f>IF(OR(F67="",NOT(ISNUMBER(F67))),"",IFERROR(VLOOKUP(F67,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H67" s="15" t="n"/>
     </row>
     <row r="68">
@@ -2319,7 +2496,10 @@
         </is>
       </c>
       <c r="F68" s="15" t="n"/>
-      <c r="G68" s="15" t="n"/>
+      <c r="G68" s="16">
+        <f>IF(OR(F68="",NOT(ISNUMBER(F68))),"",IFERROR(VLOOKUP(F68,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H68" s="15" t="n"/>
     </row>
     <row r="69">
@@ -2334,7 +2514,7 @@
           <t>Is there a documented and approved data governance model aligned with the solution's information and privacy requirements?</t>
         </is>
       </c>
-      <c r="D69" s="16" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
@@ -2345,7 +2525,10 @@
         </is>
       </c>
       <c r="F69" s="15" t="n"/>
-      <c r="G69" s="15" t="n"/>
+      <c r="G69" s="16">
+        <f>IF(OR(F69="",NOT(ISNUMBER(F69))),"",IFERROR(VLOOKUP(F69,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H69" s="15" t="n"/>
     </row>
     <row r="70">
@@ -2367,7 +2550,10 @@
         </is>
       </c>
       <c r="F70" s="15" t="n"/>
-      <c r="G70" s="15" t="n"/>
+      <c r="G70" s="16">
+        <f>IF(OR(F70="",NOT(ISNUMBER(F70))),"",IFERROR(VLOOKUP(F70,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H70" s="15" t="n"/>
     </row>
   </sheetData>
@@ -2501,7 +2687,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="16">
+        <f>IF(OR(F5="",NOT(ISNUMBER(F5))),"",IFERROR(VLOOKUP(F5,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -2523,7 +2712,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="16">
+        <f>IF(OR(F6="",NOT(ISNUMBER(F6))),"",IFERROR(VLOOKUP(F6,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -2538,7 +2730,7 @@
           <t>How well understood are data volumes, growth rates, residency requirements, and encryption posture?</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -2549,7 +2741,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="16">
+        <f>IF(OR(F7="",NOT(ISNUMBER(F7))),"",IFERROR(VLOOKUP(F7,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -2571,7 +2766,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="16">
+        <f>IF(OR(F8="",NOT(ISNUMBER(F8))),"",IFERROR(VLOOKUP(F8,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -2593,7 +2791,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="16">
+        <f>IF(OR(F9="",NOT(ISNUMBER(F9))),"",IFERROR(VLOOKUP(F9,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -2615,7 +2816,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="16">
+        <f>IF(OR(F10="",NOT(ISNUMBER(F10))),"",IFERROR(VLOOKUP(F10,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -2637,7 +2841,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="16">
+        <f>IF(OR(F11="",NOT(ISNUMBER(F11))),"",IFERROR(VLOOKUP(F11,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
@@ -2652,7 +2859,7 @@
           <t>How mature are data access controls, auditing mechanisms, and the ability to trace who accessed what and when?</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -2663,7 +2870,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="G12" s="16">
+        <f>IF(OR(F12="",NOT(ISNUMBER(F12))),"",IFERROR(VLOOKUP(F12,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H12" s="15" t="n"/>
     </row>
     <row r="13">
@@ -2685,7 +2895,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="G13" s="16">
+        <f>IF(OR(F13="",NOT(ISNUMBER(F13))),"",IFERROR(VLOOKUP(F13,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
@@ -2718,7 +2931,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",NOT(ISNUMBER(F15))),"",IFERROR(VLOOKUP(F15,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -2740,7 +2956,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",NOT(ISNUMBER(F16))),"",IFERROR(VLOOKUP(F16,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -2755,7 +2974,7 @@
           <t>Is data lifecycle governance established, covering creation, versioning, archiving, and secure disposition?</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -2766,7 +2985,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",NOT(ISNUMBER(F17))),"",IFERROR(VLOOKUP(F17,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -2788,7 +3010,10 @@
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",NOT(ISNUMBER(F18))),"",IFERROR(VLOOKUP(F18,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
@@ -2810,7 +3035,10 @@
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="G19" s="16">
+        <f>IF(OR(F19="",NOT(ISNUMBER(F19))),"",IFERROR(VLOOKUP(F19,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
@@ -2832,7 +3060,10 @@
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",NOT(ISNUMBER(F20))),"",IFERROR(VLOOKUP(F20,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -2854,7 +3085,10 @@
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",NOT(ISNUMBER(F21))),"",IFERROR(VLOOKUP(F21,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -2876,7 +3110,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",NOT(ISNUMBER(F22))),"",IFERROR(VLOOKUP(F22,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
@@ -2898,7 +3135,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="G23" s="16">
+        <f>IF(OR(F23="",NOT(ISNUMBER(F23))),"",IFERROR(VLOOKUP(F23,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
@@ -2920,7 +3160,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",NOT(ISNUMBER(F24))),"",IFERROR(VLOOKUP(F24,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
@@ -2942,7 +3185,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="G25" s="16">
+        <f>IF(OR(F25="",NOT(ISNUMBER(F25))),"",IFERROR(VLOOKUP(F25,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H25" s="15" t="n"/>
     </row>
     <row r="26">
@@ -2964,7 +3210,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="G26" s="16">
+        <f>IF(OR(F26="",NOT(ISNUMBER(F26))),"",IFERROR(VLOOKUP(F26,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H26" s="15" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
@@ -2990,18 +3239,21 @@
           <t>Has a Privacy Impact Assessment (PIA) been completed, and does the architecture reflect its recommendations?</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="G28" s="16">
+        <f>IF(OR(F28="",NOT(ISNUMBER(F28))),"",IFERROR(VLOOKUP(F28,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -3016,7 +3268,7 @@
           <t>Is Privacy by Design embedded throughout the solution, from data collection through to disposition?</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
@@ -3027,7 +3279,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="G29" s="16">
+        <f>IF(OR(F29="",NOT(ISNUMBER(F29))),"",IFERROR(VLOOKUP(F29,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -3049,7 +3304,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="G30" s="16">
+        <f>IF(OR(F30="",NOT(ISNUMBER(F30))),"",IFERROR(VLOOKUP(F30,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
@@ -3064,7 +3322,7 @@
           <t>Is encryption applied at rest, in transit, and in processing for all data at the appropriate sensitivity level?</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -3075,7 +3333,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="G31" s="16">
+        <f>IF(OR(F31="",NOT(ISNUMBER(F31))),"",IFERROR(VLOOKUP(F31,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
@@ -3090,7 +3351,7 @@
           <t>Are data sovereignty requirements met — is there full awareness of where data resides, crosses borders, and is subject to foreign law?</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -3101,7 +3362,10 @@
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="G32" s="16">
+        <f>IF(OR(F32="",NOT(ISNUMBER(F32))),"",IFERROR(VLOOKUP(F32,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
@@ -3116,7 +3380,7 @@
           <t>Are data retention and disposition policies enforced, including secure deletion and legal hold capabilities?</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Security, Privacy</t>
         </is>
@@ -3127,7 +3391,10 @@
         </is>
       </c>
       <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="G33" s="16">
+        <f>IF(OR(F33="",NOT(ISNUMBER(F33))),"",IFERROR(VLOOKUP(F33,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H33" s="15" t="n"/>
     </row>
     <row r="34">
@@ -3142,7 +3409,7 @@
           <t>How well are collection limitation principles applied — is only necessary data collected, with informed consent where required?</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
@@ -3153,7 +3420,10 @@
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="G34" s="16">
+        <f>IF(OR(F34="",NOT(ISNUMBER(F34))),"",IFERROR(VLOOKUP(F34,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H34" s="15" t="n"/>
     </row>
     <row r="35">
@@ -3168,18 +3438,21 @@
           <t>Is there a documented breach response plan, and has it been tested?</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E35" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="G35" s="16">
+        <f>IF(OR(F35="",NOT(ISNUMBER(F35))),"",IFERROR(VLOOKUP(F35,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -3194,7 +3467,7 @@
           <t>Are access controls enforced at the data level, ensuring role-based and attribute-based access is actively governed?</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -3205,7 +3478,10 @@
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="G36" s="16">
+        <f>IF(OR(F36="",NOT(ISNUMBER(F36))),"",IFERROR(VLOOKUP(F36,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H36" s="15" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
@@ -3238,7 +3514,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="G38" s="16">
+        <f>IF(OR(F38="",NOT(ISNUMBER(F38))),"",IFERROR(VLOOKUP(F38,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -3260,7 +3539,10 @@
         </is>
       </c>
       <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="G39" s="16">
+        <f>IF(OR(F39="",NOT(ISNUMBER(F39))),"",IFERROR(VLOOKUP(F39,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H39" s="15" t="n"/>
     </row>
     <row r="40">
@@ -3275,7 +3557,7 @@
           <t>How accessible is data to authorized consumers, including other departments, partners, and (where appropriate) the public?</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -3286,7 +3568,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="G40" s="16">
+        <f>IF(OR(F40="",NOT(ISNUMBER(F40))),"",IFERROR(VLOOKUP(F40,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H40" s="15" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
@@ -3319,7 +3604,10 @@
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="G42" s="16">
+        <f>IF(OR(F42="",NOT(ISNUMBER(F42))),"",IFERROR(VLOOKUP(F42,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
@@ -3341,7 +3629,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="G43" s="16">
+        <f>IF(OR(F43="",NOT(ISNUMBER(F43))),"",IFERROR(VLOOKUP(F43,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H43" s="15" t="n"/>
     </row>
     <row r="44">
@@ -3363,7 +3654,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="G44" s="16">
+        <f>IF(OR(F44="",NOT(ISNUMBER(F44))),"",IFERROR(VLOOKUP(F44,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H44" s="15" t="n"/>
     </row>
     <row r="45">
@@ -3378,7 +3672,7 @@
           <t>Is there a process to ensure data governance keeps pace with legislative changes (Privacy Act, Access to Information, Bill C-27)?</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
@@ -3389,7 +3683,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="G45" s="16">
+        <f>IF(OR(F45="",NOT(ISNUMBER(F45))),"",IFERROR(VLOOKUP(F45,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H45" s="15" t="n"/>
     </row>
     <row r="46">
@@ -3404,7 +3701,7 @@
           <t>How well is data quality monitored, reported on, and escalated when thresholds are breached?</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -3415,7 +3712,10 @@
         </is>
       </c>
       <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="G46" s="16">
+        <f>IF(OR(F46="",NOT(ISNUMBER(F46))),"",IFERROR(VLOOKUP(F46,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H46" s="15" t="n"/>
     </row>
     <row r="47">
@@ -3437,7 +3737,10 @@
         </is>
       </c>
       <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="G47" s="16">
+        <f>IF(OR(F47="",NOT(ISNUMBER(F47))),"",IFERROR(VLOOKUP(F47,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H47" s="15" t="n"/>
     </row>
   </sheetData>
@@ -3570,7 +3873,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="16">
+        <f>IF(OR(F5="",NOT(ISNUMBER(F5))),"",IFERROR(VLOOKUP(F5,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -3592,7 +3898,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="16">
+        <f>IF(OR(F6="",NOT(ISNUMBER(F6))),"",IFERROR(VLOOKUP(F6,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -3614,7 +3923,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="16">
+        <f>IF(OR(F7="",NOT(ISNUMBER(F7))),"",IFERROR(VLOOKUP(F7,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -3636,7 +3948,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="16">
+        <f>IF(OR(F8="",NOT(ISNUMBER(F8))),"",IFERROR(VLOOKUP(F8,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -3651,7 +3966,7 @@
           <t>What known security vulnerabilities exist in the current solution, and what is the remediation status?</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -3662,7 +3977,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="16">
+        <f>IF(OR(F9="",NOT(ISNUMBER(F9))),"",IFERROR(VLOOKUP(F9,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -3684,7 +4002,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="16">
+        <f>IF(OR(F10="",NOT(ISNUMBER(F10))),"",IFERROR(VLOOKUP(F10,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -3706,7 +4027,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="16">
+        <f>IF(OR(F11="",NOT(ISNUMBER(F11))),"",IFERROR(VLOOKUP(F11,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
@@ -3728,7 +4052,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="G12" s="16">
+        <f>IF(OR(F12="",NOT(ISNUMBER(F12))),"",IFERROR(VLOOKUP(F12,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H12" s="15" t="n"/>
     </row>
     <row r="13">
@@ -3750,7 +4077,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="G13" s="16">
+        <f>IF(OR(F13="",NOT(ISNUMBER(F13))),"",IFERROR(VLOOKUP(F13,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
@@ -3783,7 +4113,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",NOT(ISNUMBER(F15))),"",IFERROR(VLOOKUP(F15,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -3805,7 +4138,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",NOT(ISNUMBER(F16))),"",IFERROR(VLOOKUP(F16,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -3827,7 +4163,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",NOT(ISNUMBER(F17))),"",IFERROR(VLOOKUP(F17,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -3849,7 +4188,10 @@
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",NOT(ISNUMBER(F18))),"",IFERROR(VLOOKUP(F18,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
@@ -3871,7 +4213,10 @@
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="G19" s="16">
+        <f>IF(OR(F19="",NOT(ISNUMBER(F19))),"",IFERROR(VLOOKUP(F19,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
@@ -3893,7 +4238,10 @@
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",NOT(ISNUMBER(F20))),"",IFERROR(VLOOKUP(F20,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -3915,7 +4263,10 @@
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",NOT(ISNUMBER(F21))),"",IFERROR(VLOOKUP(F21,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -3937,7 +4288,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",NOT(ISNUMBER(F22))),"",IFERROR(VLOOKUP(F22,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
@@ -3959,7 +4313,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="G23" s="16">
+        <f>IF(OR(F23="",NOT(ISNUMBER(F23))),"",IFERROR(VLOOKUP(F23,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
@@ -3981,7 +4338,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",NOT(ISNUMBER(F24))),"",IFERROR(VLOOKUP(F24,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H24" s="15" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
@@ -4007,7 +4367,7 @@
           <t>How mature is the DevSecOps pipeline — including continuous integration, continuous deployment, automated testing, and security gates?</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -4018,7 +4378,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="G26" s="16">
+        <f>IF(OR(F26="",NOT(ISNUMBER(F26))),"",IFERROR(VLOOKUP(F26,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
@@ -4033,7 +4396,7 @@
           <t>Is test coverage defined, measured, and enforced — including unit, integration, regression, performance, and security testing?</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -4044,7 +4407,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="G27" s="16">
+        <f>IF(OR(F27="",NOT(ISNUMBER(F27))),"",IFERROR(VLOOKUP(F27,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H27" s="15" t="n"/>
     </row>
     <row r="28">
@@ -4066,7 +4432,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="G28" s="16">
+        <f>IF(OR(F28="",NOT(ISNUMBER(F28))),"",IFERROR(VLOOKUP(F28,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -4081,18 +4450,21 @@
           <t>Are accessibility standards (WCAG 2.1 AA or equivalent) embedded in the development and QA process?</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="G29" s="16">
+        <f>IF(OR(F29="",NOT(ISNUMBER(F29))),"",IFERROR(VLOOKUP(F29,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -4108,13 +4480,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="G30" s="16">
+        <f>IF(OR(F30="",NOT(ISNUMBER(F30))),"",IFERROR(VLOOKUP(F30,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
@@ -4136,7 +4511,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="G31" s="16">
+        <f>IF(OR(F31="",NOT(ISNUMBER(F31))),"",IFERROR(VLOOKUP(F31,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
@@ -4158,7 +4536,10 @@
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="G32" s="16">
+        <f>IF(OR(F32="",NOT(ISNUMBER(F32))),"",IFERROR(VLOOKUP(F32,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
@@ -4180,7 +4561,10 @@
         </is>
       </c>
       <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="G33" s="16">
+        <f>IF(OR(F33="",NOT(ISNUMBER(F33))),"",IFERROR(VLOOKUP(F33,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
@@ -4206,7 +4590,7 @@
           <t>Has a multi-disciplinary team — including business, security, privacy, data, and technology — been engaged in solution design?</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Security, Privacy</t>
         </is>
@@ -4217,7 +4601,10 @@
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="G35" s="16">
+        <f>IF(OR(F35="",NOT(ISNUMBER(F35))),"",IFERROR(VLOOKUP(F35,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -4232,7 +4619,7 @@
           <t>Were enterprise contracts and procurement pathways (GC-wide standing offers, task authorizations) explored before custom sourcing?</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -4243,7 +4630,10 @@
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="G36" s="16">
+        <f>IF(OR(F36="",NOT(ISNUMBER(F36))),"",IFERROR(VLOOKUP(F36,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
@@ -4265,7 +4655,10 @@
         </is>
       </c>
       <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="G37" s="16">
+        <f>IF(OR(F37="",NOT(ISNUMBER(F37))),"",IFERROR(VLOOKUP(F37,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H37" s="15" t="n"/>
     </row>
     <row r="38">
@@ -4280,7 +4673,7 @@
           <t>Is a Total Cost of Ownership (TCO) model available that includes build, operate, maintain, licensing, and exit costs?</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -4291,7 +4684,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="G38" s="16">
+        <f>IF(OR(F38="",NOT(ISNUMBER(F38))),"",IFERROR(VLOOKUP(F38,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -4306,7 +4702,7 @@
           <t>How well are digital sovereignty considerations addressed — are GC data and systems protected from foreign jurisdiction risk?</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -4317,7 +4713,10 @@
         </is>
       </c>
       <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="G39" s="16">
+        <f>IF(OR(F39="",NOT(ISNUMBER(F39))),"",IFERROR(VLOOKUP(F39,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H39" s="15" t="n"/>
     </row>
     <row r="40">
@@ -4339,7 +4738,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="G40" s="16">
+        <f>IF(OR(F40="",NOT(ISNUMBER(F40))),"",IFERROR(VLOOKUP(F40,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H40" s="15" t="n"/>
     </row>
     <row r="41">
@@ -4354,7 +4756,7 @@
           <t>How well does the solution avoid unnecessary duplication with existing GC capabilities and investments?</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -4365,7 +4767,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="G41" s="16">
+        <f>IF(OR(F41="",NOT(ISNUMBER(F41))),"",IFERROR(VLOOKUP(F41,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H41" s="15" t="n"/>
     </row>
     <row r="42">
@@ -4387,7 +4792,10 @@
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="G42" s="16">
+        <f>IF(OR(F42="",NOT(ISNUMBER(F42))),"",IFERROR(VLOOKUP(F42,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
@@ -4409,7 +4817,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="G43" s="16">
+        <f>IF(OR(F43="",NOT(ISNUMBER(F43))),"",IFERROR(VLOOKUP(F43,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H43" s="15" t="n"/>
     </row>
     <row r="44">
@@ -4424,7 +4835,7 @@
           <t>How well are supply chain security risks addressed in the sourcing and integration of third-party components?</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -4435,7 +4846,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="G44" s="16">
+        <f>IF(OR(F44="",NOT(ISNUMBER(F44))),"",IFERROR(VLOOKUP(F44,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H44" s="15" t="n"/>
     </row>
   </sheetData>
@@ -4567,7 +4981,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="16">
+        <f>IF(OR(F5="",NOT(ISNUMBER(F5))),"",IFERROR(VLOOKUP(F5,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -4589,7 +5006,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="16">
+        <f>IF(OR(F6="",NOT(ISNUMBER(F6))),"",IFERROR(VLOOKUP(F6,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -4611,7 +5031,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="16">
+        <f>IF(OR(F7="",NOT(ISNUMBER(F7))),"",IFERROR(VLOOKUP(F7,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -4633,7 +5056,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="16">
+        <f>IF(OR(F8="",NOT(ISNUMBER(F8))),"",IFERROR(VLOOKUP(F8,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -4655,7 +5081,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="16">
+        <f>IF(OR(F9="",NOT(ISNUMBER(F9))),"",IFERROR(VLOOKUP(F9,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -4677,7 +5106,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="16">
+        <f>IF(OR(F10="",NOT(ISNUMBER(F10))),"",IFERROR(VLOOKUP(F10,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -4699,7 +5131,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="16">
+        <f>IF(OR(F11="",NOT(ISNUMBER(F11))),"",IFERROR(VLOOKUP(F11,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H11" s="15" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
@@ -4732,7 +5167,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="G13" s="16">
+        <f>IF(OR(F13="",NOT(ISNUMBER(F13))),"",IFERROR(VLOOKUP(F13,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H13" s="15" t="n"/>
     </row>
     <row r="14">
@@ -4747,7 +5185,7 @@
           <t>Is the decision between shared and dedicated hardware documented with supporting rationale for cost, isolation, and performance?</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -4758,7 +5196,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="G14" s="16">
+        <f>IF(OR(F14="",NOT(ISNUMBER(F14))),"",IFERROR(VLOOKUP(F14,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H14" s="15" t="n"/>
     </row>
     <row r="15">
@@ -4780,7 +5221,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",NOT(ISNUMBER(F15))),"",IFERROR(VLOOKUP(F15,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -4802,7 +5246,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",NOT(ISNUMBER(F16))),"",IFERROR(VLOOKUP(F16,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -4824,7 +5271,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",NOT(ISNUMBER(F17))),"",IFERROR(VLOOKUP(F17,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -4846,7 +5296,10 @@
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",NOT(ISNUMBER(F18))),"",IFERROR(VLOOKUP(F18,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
@@ -4862,13 +5315,16 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="G19" s="16">
+        <f>IF(OR(F19="",NOT(ISNUMBER(F19))),"",IFERROR(VLOOKUP(F19,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
@@ -4890,7 +5346,10 @@
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",NOT(ISNUMBER(F20))),"",IFERROR(VLOOKUP(F20,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -4912,7 +5371,10 @@
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",NOT(ISNUMBER(F21))),"",IFERROR(VLOOKUP(F21,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -4934,7 +5396,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",NOT(ISNUMBER(F22))),"",IFERROR(VLOOKUP(F22,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H22" s="15" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
@@ -4967,7 +5432,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",NOT(ISNUMBER(F24))),"",IFERROR(VLOOKUP(F24,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
@@ -4989,7 +5457,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="G25" s="16">
+        <f>IF(OR(F25="",NOT(ISNUMBER(F25))),"",IFERROR(VLOOKUP(F25,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H25" s="15" t="n"/>
     </row>
     <row r="26">
@@ -5011,7 +5482,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="G26" s="16">
+        <f>IF(OR(F26="",NOT(ISNUMBER(F26))),"",IFERROR(VLOOKUP(F26,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
@@ -5033,7 +5507,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="G27" s="16">
+        <f>IF(OR(F27="",NOT(ISNUMBER(F27))),"",IFERROR(VLOOKUP(F27,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H27" s="15" t="n"/>
     </row>
     <row r="28">
@@ -5048,7 +5525,7 @@
           <t>Is there a documented plan and roadmap for quantum and post-quantum cryptography readiness?</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -5059,7 +5536,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="G28" s="16">
+        <f>IF(OR(F28="",NOT(ISNUMBER(F28))),"",IFERROR(VLOOKUP(F28,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -5081,7 +5561,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="G29" s="16">
+        <f>IF(OR(F29="",NOT(ISNUMBER(F29))),"",IFERROR(VLOOKUP(F29,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -5103,7 +5586,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="G30" s="16">
+        <f>IF(OR(F30="",NOT(ISNUMBER(F30))),"",IFERROR(VLOOKUP(F30,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H30" s="15" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
@@ -5136,7 +5622,10 @@
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="G32" s="16">
+        <f>IF(OR(F32="",NOT(ISNUMBER(F32))),"",IFERROR(VLOOKUP(F32,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
@@ -5151,7 +5640,7 @@
           <t>Is the solution's data sovereignty posture clearly documented, including data residency and foreign access risk mitigation?</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -5162,7 +5651,10 @@
         </is>
       </c>
       <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="G33" s="16">
+        <f>IF(OR(F33="",NOT(ISNUMBER(F33))),"",IFERROR(VLOOKUP(F33,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H33" s="15" t="n"/>
     </row>
     <row r="34">
@@ -5177,7 +5669,7 @@
           <t>How mature is the zero-trust security architecture — is authentication, authorization, and segmentation enforced throughout?</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -5188,7 +5680,10 @@
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="G34" s="16">
+        <f>IF(OR(F34="",NOT(ISNUMBER(F34))),"",IFERROR(VLOOKUP(F34,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H34" s="15" t="n"/>
     </row>
     <row r="35">
@@ -5203,7 +5698,7 @@
           <t>Is encryption applied appropriately at rest, in transit, and in processing, using GC-approved cryptographic standards?</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -5214,7 +5709,10 @@
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="G35" s="16">
+        <f>IF(OR(F35="",NOT(ISNUMBER(F35))),"",IFERROR(VLOOKUP(F35,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -5229,18 +5727,21 @@
           <t>Has a Threat and Risk Assessment (TRA) or Security Assessment and Authorization (SA&amp;A) been completed and reflected in design?</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="G36" s="16">
+        <f>IF(OR(F36="",NOT(ISNUMBER(F36))),"",IFERROR(VLOOKUP(F36,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
@@ -5255,7 +5756,7 @@
           <t>Are security controls validated through automated security testing, vulnerability scanning, and penetration testing?</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -5266,7 +5767,10 @@
         </is>
       </c>
       <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="G37" s="16">
+        <f>IF(OR(F37="",NOT(ISNUMBER(F37))),"",IFERROR(VLOOKUP(F37,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H37" s="15" t="n"/>
     </row>
     <row r="38">
@@ -5288,7 +5792,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="G38" s="16">
+        <f>IF(OR(F38="",NOT(ISNUMBER(F38))),"",IFERROR(VLOOKUP(F38,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -5303,7 +5810,7 @@
           <t>Are GC Cloud Guardrails and security baseline configurations implemented and continuously validated?</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -5314,7 +5821,10 @@
         </is>
       </c>
       <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="G39" s="16">
+        <f>IF(OR(F39="",NOT(ISNUMBER(F39))),"",IFERROR(VLOOKUP(F39,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H39" s="15" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
@@ -5347,7 +5857,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="G41" s="16">
+        <f>IF(OR(F41="",NOT(ISNUMBER(F41))),"",IFERROR(VLOOKUP(F41,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H41" s="15" t="n"/>
     </row>
     <row r="42">
@@ -5369,7 +5882,10 @@
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="G42" s="16">
+        <f>IF(OR(F42="",NOT(ISNUMBER(F42))),"",IFERROR(VLOOKUP(F42,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
@@ -5384,7 +5900,7 @@
           <t>How mature is the FinOps practice — are cloud and infrastructure costs tracked, attributed, optimized, and reported?</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -5395,7 +5911,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="G43" s="16">
+        <f>IF(OR(F43="",NOT(ISNUMBER(F43))),"",IFERROR(VLOOKUP(F43,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H43" s="15" t="n"/>
     </row>
     <row r="44">
@@ -5417,7 +5936,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="G44" s="16">
+        <f>IF(OR(F44="",NOT(ISNUMBER(F44))),"",IFERROR(VLOOKUP(F44,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H44" s="15" t="n"/>
     </row>
     <row r="45">
@@ -5432,7 +5954,7 @@
           <t>Are resource governance policies enforced — including tagging, cost allocation, and access to shared infrastructure?</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -5443,7 +5965,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="G45" s="16">
+        <f>IF(OR(F45="",NOT(ISNUMBER(F45))),"",IFERROR(VLOOKUP(F45,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H45" s="15" t="n"/>
     </row>
     <row r="46">
@@ -5458,18 +5983,21 @@
           <t>Is there a continuous business need (CBN) process to evaluate whether infrastructure investment remains justified?</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="18" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="G46" s="16">
+        <f>IF(OR(F46="",NOT(ISNUMBER(F46))),"",IFERROR(VLOOKUP(F46,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H46" s="15" t="n"/>
     </row>
     <row r="47">
@@ -5491,7 +6019,10 @@
         </is>
       </c>
       <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="G47" s="16">
+        <f>IF(OR(F47="",NOT(ISNUMBER(F47))),"",IFERROR(VLOOKUP(F47,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H47" s="15" t="n"/>
     </row>
   </sheetData>
@@ -5542,39 +6073,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>Colour</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="A3" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -5586,17 +6115,15 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Dark Red</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>Critical Gaps</t>
         </is>
@@ -5608,17 +6135,15 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Fragmented</t>
         </is>
@@ -5630,17 +6155,15 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="A6" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Emergent</t>
         </is>
@@ -5652,17 +6175,15 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="A7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Orange-Yellow</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Defined</t>
         </is>
@@ -5674,17 +6195,15 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Integrated</t>
         </is>
@@ -5696,17 +6215,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="A9" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Yellow-Green</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Managed</t>
         </is>
@@ -5718,17 +6235,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="A10" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Scalable &amp; Secure</t>
         </is>
@@ -5740,17 +6255,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Dark Green</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>Agile/Extensible</t>
         </is>
@@ -5762,17 +6275,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="A12" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Predictive</t>
         </is>
@@ -5784,17 +6295,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Purple</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Symbiotic</t>
         </is>
@@ -5836,14 +6345,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Scores below are automatically calculated from the four architecture worksheets. Enter scores on each tab to populate this dashboard.</t>
         </is>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
+      <c r="B2" s="31" t="n"/>
+      <c r="C2" s="31" t="n"/>
+      <c r="D2" s="31" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -5940,18 +6449,18 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>OVERALL GC EA MATURITY SCORE</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n"/>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Awaiting input</t>
         </is>
       </c>
-      <c r="D10" s="31" t="n"/>
+      <c r="D10" s="32" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -6034,7 +6543,7 @@
       <c r="D17" s="12" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>This tab is your own Summary Dashboard, reproduced so nothing is missing from this copy. It does not calculate here: this workbook is for the Categories columns, and the scoring happens in the tool.</t>
         </is>
